--- a/modules/trading/reports/export/daily_report_2026-01-31.xlsx
+++ b/modules/trading/reports/export/daily_report_2026-01-31.xlsx
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>82770</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>-2.31%</t>
+        <v>82659</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일주일간 상승 (56.5 → 60.7, +7.5%) - 낮은 채권 변동성 (안정적)</t>
+          <t>일주일간 횡보 (56.5 → 59.2, +4.8%) - 낮은 채권 변동성 (안정적)</t>
         </is>
       </c>
     </row>
@@ -887,11 +887,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>60.73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>59.2</v>
       </c>
     </row>
   </sheetData>
@@ -964,11 +974,11 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
     </row>
@@ -979,11 +989,11 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
     </row>
@@ -994,11 +1004,11 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1125,7 @@
 [MOVE - 채권 변동성]
 • 현재: 60.7
 • 수준: 정상 범위
-• 주간: 일주일간 상승 (56.5 → 60.7, +7.5%) - 낮은 채권 변동성 (안정적)
+• 주간: 일주일간 횡보 (56.5 → 59.2, +4.8%) - 낮은 채권 변동성 (안정적)
 • 해석: MOVE 80 미만으로 금리 급변 리스크 낮음
 ## 금리 환경
 [SOFR]
@@ -1133,8 +1143,8 @@
 • EUR/USD: 1.1900 - 달러 강세
 • USD/JPY: 154.73 (BOJ 개입 경계)
 [암호화폐]
-• Bitcoin: $82,770 (-2.31%)
-• 해석: 소폭 하락
+• Bitcoin: $82,659 (+0.03%)
+• 해석: 횡보
 ## 종목별 상세 분석
 [VIX] 17.0 (+0.77%) - 정상 범위
 • 의미: S&amp;P 500 옵션 내재변동성 (공포지수)
@@ -1164,16 +1174,16 @@
 • 의미: 위험선호 지표. 엔화는 전통적 안전통화.
 • BOJ: 일본은행 정책 변화 시 급변동 가능.
 • 개입 경계: 155 이상 시 구두/실제 개입 가능.
-[Bitcoin] $82,770 (-2.31%)
+[Bitcoin] $82,659 (+0.03%)
 • 의미: 디지털 자산 대장주. 위험선호 심리 바로미터.
-• 기술적: 지지 $74,493 / 저항 $91,047
+• 기술적: 지지 $74,393 / 저항 $90,925
 • 상관관계: 나스닥과 높은 상관 (0.6-0.8)
-• 전망: 소폭 하락. 차익실현 또는 위험회피.
+• 전망: 횡보. 방향성 탐색 중.
 ## 핵심 경제지표
 - 연방기금금리: 3.72% (2025-12-01)
-- 10년 국채 수익률: 4.26% (2026-01-28)
-- 2년 국채 수익률: 3.56% (2026-01-28)
-- 10Y-2Y 스프레드: 0.71% (2026-01-29)
+- 10년 국채 수익률: 4.24% (2026-01-29)
+- 2년 국채 수익률: 3.53% (2026-01-29)
+- 10Y-2Y 스프레드: 0.74% (2026-01-30)
 - CPI: 326.03% (2025-12-01)
 ## 내일 전망
 - 내일 예정된 주요 이벤트 없음
